--- a/artfynd/A 40777-2023 artfynd.xlsx
+++ b/artfynd/A 40777-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40777-2023 artfynd.xlsx
+++ b/artfynd/A 40777-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1600,6 +1600,130 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>124822196</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57393</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100011</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kungsörn</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Aquila chrysaetos</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Knivslidmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>516056</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7018124</v>
+      </c>
+      <c r="S10" t="n">
+        <v>48</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40777-2023 artfynd.xlsx
+++ b/artfynd/A 40777-2023 artfynd.xlsx
@@ -1606,7 +1606,7 @@
         <v>124822196</v>
       </c>
       <c r="B10" t="n">
-        <v>57393</v>
+        <v>57548</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 40777-2023 artfynd.xlsx
+++ b/artfynd/A 40777-2023 artfynd.xlsx
@@ -1608,11 +1608,6 @@
       <c r="B10" t="n">
         <v>57548</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>NT</t>

--- a/artfynd/A 40777-2023 artfynd.xlsx
+++ b/artfynd/A 40777-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56220147</v>
+        <v>56220151</v>
       </c>
       <c r="B2" t="n">
-        <v>78472</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>388</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>516202.201539672</v>
+        <v>516101</v>
       </c>
       <c r="R2" t="n">
-        <v>7018173.595274681</v>
+        <v>7018159</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2015-06-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>56220153</v>
+        <v>56220149</v>
       </c>
       <c r="B3" t="n">
-        <v>89952</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>760</v>
+        <v>73</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516005.1594730491</v>
+        <v>516146</v>
       </c>
       <c r="R3" t="n">
-        <v>7017939.121818042</v>
+        <v>7017946</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,22 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-06-24</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-06-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>56220152</v>
+        <v>56220147</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80298</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>388</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516034.822687768</v>
+        <v>516202</v>
       </c>
       <c r="R4" t="n">
-        <v>7017953.216260512</v>
+        <v>7018174</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,22 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2015-06-24</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2015-06-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>56220151</v>
+        <v>56220153</v>
       </c>
       <c r="B5" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>760</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516101.3675792581</v>
+        <v>516005</v>
       </c>
       <c r="R5" t="n">
-        <v>7018159.143135913</v>
+        <v>7017939</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,22 +1043,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,12 +1082,7 @@
         <v>56220146</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516111.5026822088</v>
+        <v>516112</v>
       </c>
       <c r="R6" t="n">
-        <v>7018294.150302975</v>
+        <v>7018294</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,19 +1147,9 @@
           <t>2015-06-23</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>56220149</v>
+        <v>124822196</v>
       </c>
       <c r="B7" t="n">
-        <v>89652</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,37 +1191,49 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>73</v>
+        <v>100011</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Knivslidsmyren, Jmt</t>
+          <t>Knivslidmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516146.1353694964</v>
+        <v>516056</v>
       </c>
       <c r="R7" t="n">
-        <v>7017945.675014911</v>
+        <v>7018124</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1325,22 +1257,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,31 +1287,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sebastian Acker</t>
+          <t>Erik Söderhjelm</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sebastian Acker</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>56220150</v>
+        <v>56220152</v>
       </c>
       <c r="B8" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,21 +1310,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1411,10 +1334,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516132.1451996103</v>
+        <v>516035</v>
       </c>
       <c r="R8" t="n">
-        <v>7017950.553648027</v>
+        <v>7017953</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,22 +1364,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1490,12 +1403,7 @@
         <v>56220148</v>
       </c>
       <c r="B9" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1527,10 +1435,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516281.0102476821</v>
+        <v>516281</v>
       </c>
       <c r="R9" t="n">
-        <v>7018089.41802184</v>
+        <v>7018089</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1560,19 +1468,9 @@
           <t>2015-06-23</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2015-06-23</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,60 +1501,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124822196</v>
+        <v>56220150</v>
       </c>
       <c r="B10" t="n">
-        <v>57548</v>
+        <v>80392</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100011</v>
+        <v>229497</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Knivslidmyren, Jmt</t>
+          <t>Knivslidsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516056</v>
+        <v>516132</v>
       </c>
       <c r="R10" t="n">
-        <v>7018124</v>
+        <v>7017951</v>
       </c>
       <c r="S10" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1680,22 +1566,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:51</t>
+          <t>2015-06-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:51</t>
+          <t>2015-06-23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,15 +1586,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erik Söderhjelm</t>
+          <t>Sebastian Acker</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erik Söderhjelm</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40777-2023 artfynd.xlsx
+++ b/artfynd/A 40777-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56220151</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56220149</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56220147</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56220153</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56220146</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1296,6 +1326,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124822196</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1397,6 +1432,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56220152</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1498,6 +1538,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56220148</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1599,8 +1644,24 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56220150</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>